--- a/output/pdf_financials_xlsx/OZ.xlsx
+++ b/output/pdf_financials_xlsx/OZ.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.310838</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.310838</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.310838</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.310838</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.310838</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3365,10 +3365,10 @@
         <v>2.266317</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.270167</v>
+        <v>0.155055</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.278336</v>
       </c>
     </row>
     <row r="93">
@@ -5656,7 +5656,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -17794,13 +17798,13 @@
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>0.053256</v>
+        <v>-0.053256</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>0.204273</v>
+        <v>-0.204273</v>
       </c>
       <c r="G235" s="5" t="n">
-        <v>0.310838</v>
+        <v>-0.310838</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OZ.xlsx
+++ b/output/pdf_financials_xlsx/OZ.xlsx
@@ -703,16 +703,16 @@
         <v>0.02825</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.031592</v>
+        <v>0.310838</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.221786</v>
+        <v>3.029166</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.505525</v>
+        <v>2.737222</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.329575</v>
+        <v>1.200593</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.830794</v>
@@ -734,16 +734,16 @@
         <v>-0.02825</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.031592</v>
+        <v>-0.310838</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.221786</v>
+        <v>-3.029166</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.505525</v>
+        <v>-2.737222</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.329575</v>
+        <v>-1.200593</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.830794</v>
@@ -768,19 +768,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.028138</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.026513</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.06498900000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.038408</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.045065</v>
       </c>
     </row>
     <row r="13">
@@ -1269,19 +1269,19 @@
         <v>-0.310838</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.990716</v>
+        <v>-3.018854</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.739174</v>
+        <v>-2.765687</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-12.253104</v>
+        <v>-12.318093</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.8058110000000001</v>
+        <v>-0.8442190000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-17.274151</v>
+        <v>-17.319216</v>
       </c>
     </row>
     <row r="28">
@@ -1331,19 +1331,19 @@
         <v>-0.310838</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.990716</v>
+        <v>-3.018854</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.739174</v>
+        <v>-2.765687</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-12.253104</v>
+        <v>-12.318093</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.80002</v>
+        <v>-0.838428</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-17.27381</v>
+        <v>-17.318875</v>
       </c>
     </row>
     <row r="30">
@@ -1485,28 +1485,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.351969</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.214871</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.13098</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.80209</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.056655</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.312361</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.08368399999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.948127</v>
       </c>
     </row>
     <row r="35">
@@ -1547,28 +1547,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.351969</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.214871</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.13098</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.80209</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.056655</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.312361</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.08368399999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.948127</v>
       </c>
     </row>
     <row r="37">
@@ -1919,28 +1919,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.351969</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.229991</v>
+        <v>0.01512</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.13707</v>
+        <v>0.00609</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.227927</v>
+        <v>0.425837</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.145989</v>
+        <v>0.089334</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.421722</v>
+        <v>0.109361</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.583467</v>
+        <v>2.499783</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.03012</v>
+        <v>0.081993</v>
       </c>
     </row>
     <row r="49">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">

--- a/output/pdf_financials_xlsx/OZ.xlsx
+++ b/output/pdf_financials_xlsx/OZ.xlsx
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.08529200000000001</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.531861</v>
       </c>
     </row>
     <row r="65">
@@ -2542,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.030684</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.250911</v>
       </c>
     </row>
     <row r="68">
@@ -3921,16 +3921,16 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035972</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003907</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>0.001926</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -4485,33 +4485,23 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0.14015</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>10.823726</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H129" s="3" t="n">
         <v>0</v>
@@ -4660,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035972</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003907</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001926</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -4681,36 +4671,26 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.000531</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.23504</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.064581</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.978317</v>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.014289</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-1.952472</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-0.902369</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.951031</v>
+        <v>-0.951531</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.39583</v>
@@ -9156,7 +9136,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -11544,7 +11528,11 @@
           <t>Net cash generated (used) in operating activities $</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>-0.000531</v>
       </c>
@@ -11692,7 +11680,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
